--- a/r5-TC-FHIR-AG-Scheduling-R5-13-Docu-findHSP/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-13-Docu-findHSP/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T15:50:20+00:00</t>
+    <t>2025-03-08T16:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
